--- a/ORDIA_公開前チェックリスト.xlsx
+++ b/ORDIA_公開前チェックリスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahib\Desktop\Claude\Onevio Lp\Onevio_ORDIA_LP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04C559FA-2354-4993-9EA3-DF581844AD81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6350FAC-6F76-4D0D-B497-9A7F9967C995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93472CE4-34B8-4BAC-B2BD-FA0AF206D8C9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{630D395C-A9E9-4F18-B0B4-7F0337B51EEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
   <si>
     <t>ORDIA 第一弾LP 公開前チェックリスト（月曜まで社内チェック → 水曜公開）</t>
   </si>
@@ -57,165 +57,168 @@
     <t>備考</t>
   </si>
   <si>
-    <t>A-1 利用規約</t>
+    <t>利用規約</t>
+  </si>
+  <si>
+    <t>第1条（適用）｜「個別契約が利用規約より優先される」としています。大口のお客様と個別契約を結ぶ運用と矛盾しないか見てください。</t>
+  </si>
+  <si>
+    <t>法務／営業</t>
+  </si>
+  <si>
+    <t>第6条（サービスの停止・中断）｜「月の稼働率が99%を下回ったら翌月分を減額」と約束しています。本当に約束できるか、細かい条件（SLA）は別途決める必要があります。</t>
+  </si>
+  <si>
+    <t>法務／開発</t>
+  </si>
+  <si>
+    <t>第7条（料金・支払）｜支払いが遅れたときの遅延損害金を「年14.6%」としています。この率でよいか確認してください。</t>
+  </si>
+  <si>
+    <t>法務／顧問</t>
   </si>
   <si>
     <t>第8条（免責事項）｜損害賠償の上限を「直近3ヶ月に払った利用料の合計」にしています。50円/ファイルだと上限がかなり小さくなりますが、それで会社として問題ないか、お客様も納得するか確認してください。</t>
   </si>
   <si>
-    <t>法務／顧問</t>
-  </si>
-  <si>
     <t>第8条（免責事項）｜AIの解析結果は「参考情報で、最終判断はお客様が確認する」という書き方です。誤解析でクレームが来たときに、この書き方で守れるか見てください。</t>
   </si>
   <si>
-    <t>第6条（サービスの停止・中断）｜「月の稼働率が99%を下回ったら翌月分を減額」と約束しています。本当に約束できるか、細かい条件（SLA）は別途決める必要があります。</t>
-  </si>
-  <si>
-    <t>法務／開発</t>
-  </si>
-  <si>
-    <t>第7条（料金・支払）｜支払いが遅れたときの遅延損害金を「年14.6%」としています。この率でよいか確認してください。</t>
-  </si>
-  <si>
     <t>第11条（解約・契約終了）｜解約は30日前通知、重大な違反があれば30日前通知で解除（直せない違反は即時）。この条件で自社の運用と合うか見てください。</t>
   </si>
   <si>
-    <t>法務／営業</t>
-  </si>
-  <si>
     <t>第11条（解約・契約終了）｜契約終了後は「30日間ダウンロード可→その後安全に削除→希望があれば削除証明書を発行」。この運用を実際に守れるか確認してください。</t>
   </si>
   <si>
-    <t>第1条（適用）｜「個別契約が利用規約より優先される」としています。大口のお客様と個別契約を結ぶ運用と矛盾しないか見てください。</t>
-  </si>
-  <si>
     <t>第15条（準拠法・管轄）｜もめ事は「日本の法律・東京地方裁判所」で扱うとしています。これでよいか確認してください。</t>
   </si>
   <si>
-    <t>A-2 プライバシーポリシー</t>
+    <t>プライバシーポリシー</t>
+  </si>
+  <si>
+    <t>第1条・第10条（事業者情報・お問い合わせ窓口）｜個人情報保護管理者を置き、窓口を info@sagbrain.com にしています。実際に対応できる人・体制があるか確認してください。</t>
+  </si>
+  <si>
+    <t>管理</t>
   </si>
   <si>
     <t>第3条（利用目的）｜「お客様のデータを、同意なしにAIの学習や外部提供には使わない」と明記しています。第2弾（本体接続版）の実装や社内方針とズレがないか確認してください。</t>
   </si>
   <si>
+    <t>第3条（利用目的）｜利用目的の(7)で「関連サービスの案内（別途同意した場合のみ）」としています。実際の運用と合っているか見てください。</t>
+  </si>
+  <si>
+    <t>第4条（第三者提供）｜外部委託先には「秘密保持・定期監査・再委託は事前承認」を求める内容です。実際にこの管理ができる体制か確認してください。</t>
+  </si>
+  <si>
+    <t>法務／管理</t>
+  </si>
+  <si>
     <t>第5条（外国にある第三者への提供）｜「データは国内保管。将来海外に出す場合は事前通知」としています。実際に使うクラウドの会社や保管場所と合っているか、会社名を書く必要があるか見てください。</t>
   </si>
   <si>
-    <t>第4条（第三者提供）｜外部委託先には「秘密保持・定期監査・再委託は事前承認」を求める内容です。実際にこの管理ができる体制か確認してください。</t>
-  </si>
-  <si>
-    <t>法務／管理</t>
-  </si>
-  <si>
     <t>第7条（保存期間および削除）｜保存期間を「契約関連5年／業務データ30日／ログ1年／問い合わせ2年」としています。実際の運用と合うか見てください。</t>
   </si>
   <si>
+    <t>第8条（Cookie・アクセス解析）｜Google Analytics等を使い、分析Cookieはオフにできると書いています。同意バナーが要るかどうか含めて確認してください。</t>
+  </si>
+  <si>
+    <t>法務／マーケ</t>
+  </si>
+  <si>
     <t>第9条（開示・訂正・利用停止等の請求）｜お客様からの開示請求などに「30日以内に回答・本人確認・実費手数料」で対応する内容です。受付する窓口や手順があるか確認してください。</t>
   </si>
   <si>
-    <t>第8条（Cookie・アクセス解析）｜Google Analytics等を使い、分析Cookieはオフにできると書いています。同意バナーが要るかどうか含めて確認してください。</t>
-  </si>
-  <si>
-    <t>法務／マーケ</t>
-  </si>
-  <si>
-    <t>第1条・第10条（事業者情報・お問い合わせ窓口）｜個人情報保護管理者を置き、窓口を info@sagbrain.com にしています。実際に対応できる人・体制があるか確認してください。</t>
-  </si>
-  <si>
-    <t>管理</t>
-  </si>
-  <si>
-    <t>第3条（利用目的）｜利用目的の(7)で「関連サービスの案内（別途同意した場合のみ）」としています。実際の運用と合っているか見てください。</t>
-  </si>
-  <si>
-    <t>A-3 共通</t>
-  </si>
-  <si>
-    <t>（両文書 共通）｜施行日を仮で「2026年7月1日」にしています。実際の公開日に合わせて、両方の日付を直してください。</t>
+    <t>規約・ポリシー共通</t>
+  </si>
+  <si>
+    <t>施行日を仮で「2026年7月1日」にしています。実際の公開日に合わせて、両方の日付を直してください。</t>
   </si>
   <si>
     <t>法務</t>
   </si>
   <si>
-    <t>（両文書 共通）｜会社情報（代表取締役 相楽 賢哉・住所・電話・info@sagbrain.com）が正しいか確認してください。</t>
-  </si>
-  <si>
-    <t>（両文書 共通）｜社名の書き方を「株式会社サグブレイン／SAGBRAIN CORPORATION」で統一しています。</t>
+    <t>会社情報（代表取締役 相楽 賢哉・住所・電話・info@sagbrain.com）が正しいか確認してください。</t>
+  </si>
+  <si>
+    <t>社名の書き方を「株式会社サグブレイン／SAGBRAIN CORPORATION」で統一しています。</t>
   </si>
   <si>
     <t>全員</t>
   </si>
   <si>
-    <t>（両文書 共通）｜第2弾（本体接続版）でも同じ規約・ポリシーを使うか決めてください（文言・URL・施行日をそろえる）。</t>
-  </si>
-  <si>
-    <t>B 料金</t>
-  </si>
-  <si>
-    <t>【LP：料金】一律「1ファイル50円（税別）・基本料0円」で最終確定してよいか確認してください。</t>
+    <t>第2弾（本体接続版）でも同じ規約・ポリシーを使うか決めてください（文言・URL・施行日をそろえる）。</t>
+  </si>
+  <si>
+    <t>LP（上→下）</t>
+  </si>
+  <si>
+    <t>【説明ビデオ（冒頭）】約1分の動画が音声付きできちんと再生されるか確認してください。</t>
+  </si>
+  <si>
+    <t>マーケ</t>
+  </si>
+  <si>
+    <t>【説明ビデオ内 効果シーン】「38%・80%」に「※当社試算」が表示されているか確認してください。</t>
+  </si>
+  <si>
+    <t>【仕組みStep3／機能／バイオの強み・対応メーカー】在庫・納期の自動照会（20社RPA）は「開発中・順次実装予定」と注記しています。この表現でよいか、実装のめどを確認してください。</t>
+  </si>
+  <si>
+    <t>開発</t>
+  </si>
+  <si>
+    <t>【「運用しながら精度向上」セクション】「使うほど賢くなる」ではなく「運用しながら精度を高める」に直しています。実態と合っているか見てください。</t>
+  </si>
+  <si>
+    <t>【差別化ポイント】マスター統合・基幹連携の説明が、実際にできることの範囲と合っているか確認してください。</t>
+  </si>
+  <si>
+    <t>【FAQ／機能】AIの精度について言い切りすぎていないか（「必ず高精度」等になっていないか）見てください。</t>
+  </si>
+  <si>
+    <t>開発／営業</t>
+  </si>
+  <si>
+    <t>【料金】一律「1ファイル50円（税別）・基本料0円」で最終確定してよいか確認してください。</t>
   </si>
   <si>
     <t>営業／開発</t>
   </si>
   <si>
-    <t>【LP：料金】第2弾（stage）は今40円表示です。50円に統一するので、開発側とそろえてください。</t>
-  </si>
-  <si>
-    <t>【LP：料金→自社ケース試算ツール】試算の前提（50円/件・手入力5分→確認1分）が営業トークと合っているか見てください。</t>
+    <t>【料金】第2弾（stage）は今40円表示です。50円に統一するので、開発側とそろえてください。</t>
+  </si>
+  <si>
+    <t>【料金→自社ケース試算ツール】試算の前提（50円/件・手入力5分→確認1分）が営業トークと合っているか見てください。</t>
   </si>
   <si>
     <t>営業</t>
   </si>
   <si>
-    <t>C 機能表現</t>
-  </si>
-  <si>
-    <t>【LP：仕組みStep3／機能／バイオの強み・対応メーカー】在庫・納期の自動照会（20社RPA）は「開発中・順次実装予定」と注記しています。この表現でよいか、実装のめどを確認してください。</t>
-  </si>
-  <si>
-    <t>開発</t>
-  </si>
-  <si>
-    <t>【LP：「運用しながら精度向上」セクション】「使うほど賢くなる」ではなく「運用しながら精度を高める」に直しています。実態と合っているか見てください。</t>
-  </si>
-  <si>
-    <t>【LP：差別化ポイント】マスター統合・基幹連携の説明が、実際にできることの範囲と合っているか確認してください。</t>
-  </si>
-  <si>
-    <t>【LP：FAQ／機能】AIの精度について言い切りすぎていないか（「必ず高精度」等になっていないか）見てください。</t>
-  </si>
-  <si>
-    <t>開発／営業</t>
-  </si>
-  <si>
-    <t>D 無料トライアル・導線</t>
-  </si>
-  <si>
-    <t>【LP：無料トライアル／お問い合わせ】「無料トライアル＝先行エントリー（フォーム）」の運用の流れを決めてください。</t>
-  </si>
-  <si>
-    <t>【LP：無料トライアル／料金】実装の無料枠「月30件」と、LPの表現がズレていないか確認してください。</t>
-  </si>
-  <si>
-    <t>【LP：お問い合わせフォーム】フォームの送信先・誰が対応するかを決めてください。</t>
-  </si>
-  <si>
-    <t>E バイオ・事例</t>
+    <t>【無料トライアル】「無料トライアル＝先行エントリー（フォーム）」の運用の流れを決めてください。</t>
+  </si>
+  <si>
+    <t>【無料トライアル／料金】実装の無料枠「月30件」と、LPの表現がズレていないか確認してください。</t>
+  </si>
+  <si>
+    <t>【バイオの皆様へ→対応メーカー】メーカー名を載せてよいか（許諾）確認してください。</t>
+  </si>
+  <si>
+    <t>【バイオの皆様へ】導入事例や数字が仮のまま載っていないか（未確定は出さない）確認してください。</t>
+  </si>
+  <si>
+    <t>【お問い合わせフォーム】フォームの送信先・誰が対応するかを決めてください。</t>
+  </si>
+  <si>
+    <t>資料・フッター</t>
+  </si>
+  <si>
+    <t>【フッター】全リンク（Onevioとは／DOG外部／エリアパートナー／規約／ポリシー／会社）が開くか確認してください。</t>
   </si>
   <si>
     <t>【フッター：エリアパートナー ページ】記載内容でよいか（正式な条件は「お問い合わせ」に誘導済み）確認してください。</t>
   </si>
   <si>
-    <t>【LP：バイオの皆様へ→対応メーカー】メーカー名を載せてよいか（許諾）確認してください。</t>
-  </si>
-  <si>
-    <t>【LP：バイオの皆様へ】導入事例や数字が仮のまま載っていないか（未確定は出さない）確認してください。</t>
-  </si>
-  <si>
-    <t>F 資料請求</t>
-  </si>
-  <si>
     <t>【資料PDF（assets）】資料の中身がLPと合っているか（料金・試算・実装予定の注記）確認してください。</t>
   </si>
   <si>
@@ -225,49 +228,34 @@
     <t>【資料請求ページ shiryou.html】フォーム送信→PDFの閲覧・ダウンロードが動くか確認してください。</t>
   </si>
   <si>
-    <t>マーケ</t>
-  </si>
-  <si>
     <t>【資料請求ページ】（任意）入力メール宛に自動でPDFを送るようにするか決めてください（FORM_ENDPOINTの設定要否）。</t>
   </si>
   <si>
-    <t>G 動画</t>
-  </si>
-  <si>
-    <t>【LP：説明ビデオ（冒頭）】約1分の動画が音声付きできちんと再生されるか確認してください。</t>
-  </si>
-  <si>
-    <t>【LP：説明ビデオ内 効果シーン】「38%・80%」に「※当社試算」が表示されているか確認してください。</t>
-  </si>
-  <si>
-    <t>H 表示・技術</t>
-  </si>
-  <si>
-    <t>【全ページ】PC・スマホで表示が崩れていないか（スマホのヘッダー重なりは修正済み）確認してください。</t>
-  </si>
-  <si>
-    <t>【フッター】全リンク（Onevioとは／DOG外部／エリアパートナー／規約／ポリシー／会社）が開くか確認してください。</t>
-  </si>
-  <si>
-    <t>【全ページ】リンク切れ・誤字脱字を目で確認してください。</t>
-  </si>
-  <si>
-    <t>【全ページのボタン】各ボタン（無料トライアル／資料請求／お問い合わせ）が正しい場所に飛ぶか確認してください。</t>
-  </si>
-  <si>
-    <t>I 公開作業</t>
-  </si>
-  <si>
-    <t>【公開作業】公開するURLを決めてください（案A：第1弾を /ordia に。第2弾と場所がかぶるので開発と調整）。</t>
+    <t>全ページ共通</t>
+  </si>
+  <si>
+    <t>PC・スマホで表示が崩れていないか（スマホのヘッダー重なりは修正済み）確認してください。</t>
+  </si>
+  <si>
+    <t>リンク切れ・誤字脱字を目で確認してください。</t>
+  </si>
+  <si>
+    <t>各ボタン（無料トライアル／資料請求／お問い合わせ）が正しい場所に飛ぶか確認してください。</t>
+  </si>
+  <si>
+    <t>公開作業</t>
+  </si>
+  <si>
+    <t>公開するURLを決めてください（案A：第1弾を /ordia に。第2弾と場所がかぶるので開発と調整）。</t>
   </si>
   <si>
     <t>インフラ／開発</t>
   </si>
   <si>
-    <t>【公開作業】公開のやり方：本番リポ Onevio-ORDIA-Sales に載せる(ECS) か、今のGitHub Pages のままか決めてください。</t>
-  </si>
-  <si>
-    <t>【公開作業】公開したあと（水曜）に、表示と動作を最終確認してください。</t>
+    <t>公開のやり方：本番リポ Onevio-ORDIA-Sales に載せる(ECS) か、今のGitHub Pages のままか決めてください。</t>
+  </si>
+  <si>
+    <t>公開したあと（水曜）に、表示と動作を最終確認してください。</t>
   </si>
 </sst>
 </file>
@@ -697,7 +685,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7FB23BD-FB7E-4AE1-B91A-EBD3C3646429}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A716E09-9CBF-462B-ABC3-14030B21EC83}">
   <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -749,7 +737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="49.5">
+    <row r="4" spans="1:8" ht="33">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -778,7 +766,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -793,17 +781,17 @@
         <v>3</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:8" ht="33">
+    <row r="7" spans="1:8" ht="49.5">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
@@ -811,10 +799,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -829,10 +817,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -850,7 +838,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -868,7 +856,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -886,7 +874,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -904,14 +892,14 @@
         <v>22</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:8" ht="49.5">
+    <row r="13" spans="1:8" ht="33">
       <c r="A13" s="5" t="s">
         <v>21</v>
       </c>
@@ -919,10 +907,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -937,10 +925,10 @@
         <v>3</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -958,14 +946,14 @@
         <v>26</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:8" ht="33">
+    <row r="16" spans="1:8" ht="49.5">
       <c r="A16" s="5" t="s">
         <v>21</v>
       </c>
@@ -973,10 +961,10 @@
         <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -991,10 +979,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -1030,7 +1018,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -1066,14 +1054,14 @@
         <v>36</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="1:8" ht="33">
+    <row r="22" spans="1:8">
       <c r="A22" s="5" t="s">
         <v>33</v>
       </c>
@@ -1102,14 +1090,14 @@
         <v>39</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:8" ht="33">
+    <row r="24" spans="1:8">
       <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
@@ -1145,7 +1133,7 @@
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="1:8" ht="33">
+    <row r="26" spans="1:8" ht="49.5">
       <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
@@ -1163,18 +1151,18 @@
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" ht="49.5">
+    <row r="27" spans="1:8" ht="33">
       <c r="A27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="5">
+        <v>4</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="5">
-        <v>1</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="D27" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1183,16 +1171,16 @@
     </row>
     <row r="28" spans="1:8" ht="33">
       <c r="A28" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -1201,16 +1189,16 @@
     </row>
     <row r="29" spans="1:8" ht="33">
       <c r="A29" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -1219,16 +1207,16 @@
     </row>
     <row r="30" spans="1:8" ht="33">
       <c r="A30" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -1237,16 +1225,16 @@
     </row>
     <row r="31" spans="1:8" ht="33">
       <c r="A31" s="5" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -1255,34 +1243,34 @@
     </row>
     <row r="32" spans="1:8" ht="33">
       <c r="A32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="5">
+        <v>9</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="5">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>55</v>
-      </c>
       <c r="D32" s="5" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" ht="33">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B33" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -1291,34 +1279,34 @@
     </row>
     <row r="34" spans="1:8" ht="33">
       <c r="A34" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
     </row>
-    <row r="35" spans="1:8" ht="33">
+    <row r="35" spans="1:8">
       <c r="A35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5">
+        <v>12</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="5">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="D35" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -1327,34 +1315,34 @@
     </row>
     <row r="36" spans="1:8" ht="33">
       <c r="A36" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
     </row>
-    <row r="37" spans="1:8" ht="33">
+    <row r="37" spans="1:8">
       <c r="A37" s="5" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -1363,16 +1351,16 @@
     </row>
     <row r="38" spans="1:8" ht="33">
       <c r="A38" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="5">
+        <v>1</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="5">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>64</v>
-      </c>
       <c r="D38" s="5" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -1381,16 +1369,16 @@
     </row>
     <row r="39" spans="1:8" ht="33">
       <c r="A39" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B39" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -1399,16 +1387,16 @@
     </row>
     <row r="40" spans="1:8" ht="33">
       <c r="A40" s="5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B40" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -1417,16 +1405,16 @@
     </row>
     <row r="41" spans="1:8" ht="33">
       <c r="A41" s="5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B41" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -1435,16 +1423,16 @@
     </row>
     <row r="42" spans="1:8" ht="33">
       <c r="A42" s="5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B42" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -1453,13 +1441,13 @@
     </row>
     <row r="43" spans="1:8" ht="33">
       <c r="A43" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B43" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>38</v>
@@ -1471,13 +1459,13 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B44" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>38</v>
@@ -1489,13 +1477,13 @@
     </row>
     <row r="45" spans="1:8" ht="33">
       <c r="A45" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="5">
+        <v>3</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="B45" s="5">
-        <v>4</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>38</v>
@@ -1507,16 +1495,16 @@
     </row>
     <row r="46" spans="1:8" ht="33">
       <c r="A46" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B46" s="5">
         <v>1</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -1525,16 +1513,16 @@
     </row>
     <row r="47" spans="1:8" ht="33">
       <c r="A47" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B47" s="5">
         <v>2</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -1543,13 +1531,13 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B48" s="5">
         <v>3</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>38</v>
@@ -1560,13 +1548,13 @@
       <c r="H48" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H3" xr:uid="{D7FB23BD-FB7E-4AE1-B91A-EBD3C3646429}"/>
+  <autoFilter ref="A3:H3" xr:uid="{1A716E09-9CBF-462B-ABC3-14030B21EC83}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E48" xr:uid="{7E887A6B-BA43-4B0B-AF6B-918A16D05933}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E48" xr:uid="{4F0B18C3-E9BB-4D4C-9D19-3CA5B09CF6D3}">
       <formula1>"未着手,確認中,OK,要修正"</formula1>
     </dataValidation>
   </dataValidations>
